--- a/sampleprojects/CorporateTax/excel/states/NJ_corp.xlsx
+++ b/sampleprojects/CorporateTax/excel/states/NJ_corp.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="117">
   <si>
     <t>DT: Determine NJ Filing Requirement</t>
   </si>
@@ -134,13 +134,13 @@
     <t>Calculate NJ state additions and subtractions; Calculate NJ state-specific income adjustments</t>
   </si>
   <si>
-    <t>set apportionment.state_additions = 0.0; set apportionment.state_subtractions = 0.0; set result.nj_entire_net_income = apportionment.state_taxable_income;</t>
+    <t>set apportionment.state_additions = 0.0; set apportionment.state_subtractions = 0.0; set nj_result.entire_net_income = apportionment.state_taxable_income;</t>
   </si>
   <si>
     <t>No nexus - zero adjustments; No nexus - no state adjustments calculated</t>
   </si>
   <si>
-    <t>set apportionment.state_additions = 0.0; set apportionment.state_subtractions = 0.0; set result.nj_entire_net_income = 0.0;</t>
+    <t>set apportionment.state_additions = 0.0; set apportionment.state_subtractions = 0.0; set nj_result.entire_net_income = 0.0;</t>
   </si>
   <si>
     <t>NJ state-specific income adjustments</t>
@@ -170,7 +170,7 @@
     <t>Calculate NJ tax at 9% base rate; Calculate NJ state tax at 9% base rate, subtract credits</t>
   </si>
   <si>
-    <t>set apportionment.state_tax = the maximum of (apportionment.state_taxable_income * apportionment.state_tax_rate - apportionment.state_credits) and (0.0); set apportionment.state_refund_or_owed = apportionment.state_payments - apportionment.state_tax;</t>
+    <t>set apportionment.state_tax = the maximum of (apportionment.state_taxable_income * nj_apportionment.state_tax_rate - apportionment.state_credits) and (0.0); set apportionment.state_refund_or_owed = apportionment.state_payments - apportionment.state_tax;</t>
   </si>
   <si>
     <t>No nexus - no tax; No NJ nexus - zero tax and refund payments</t>
@@ -203,7 +203,7 @@
     <t>Entire net income exceeds $1,000,000 surtax threshold; result.nj_entire_net_income &gt; result.nj_surtax_threshold</t>
   </si>
   <si>
-    <t>result.nj_entire_net_income &gt; result.nj_surtax_threshold</t>
+    <t>nj_result.entire_net_income &gt; nj_result.surtax_threshold</t>
   </si>
   <si>
     <t>Has positive tax base for surtax calculation</t>
@@ -212,13 +212,13 @@
     <t>Calculate NJ surtax for large corporations; Calculate NJ surtax at 2.5% for income &gt; $1M</t>
   </si>
   <si>
-    <t>set result.nj_surtax = result.nj_entire_net_income * result.nj_surtax_rate; set apportionment.state_tax = apportionment.state_tax + result.nj_surtax; set apportionment.state_refund_or_owed = apportionment.state_payments - apportionment.state_tax;</t>
+    <t>set nj_result.surtax = nj_result.entire_net_income * nj_result.surtax_rate; set apportionment.state_tax = apportionment.state_tax + nj_result.surtax; set apportionment.state_refund_or_owed = apportionment.state_payments - apportionment.state_tax;</t>
   </si>
   <si>
     <t>No surtax - below threshold; No NJ surtax - income below threshold</t>
   </si>
   <si>
-    <t>set result.nj_surtax = 0.0;</t>
+    <t>set nj_result.surtax = 0.0;</t>
   </si>
   <si>
     <t>No surtax - no nexus; No NJ surtax - no NJ nexus</t>
@@ -281,10 +281,10 @@
     <t>Reference</t>
   </si>
   <si>
-    <t>apportionment</t>
-  </si>
-  <si>
-    <t>(8 attributes)</t>
+    <t>nj_apportionment</t>
+  </si>
+  <si>
+    <t>(4 attributes)</t>
   </si>
   <si>
     <t>apportionment_formula</t>
@@ -314,76 +314,46 @@
     <t>Economic nexus gross receipts threshold - NJ uses standard $100K threshold</t>
   </si>
   <si>
-    <t>state_additions</t>
+    <t>state_tax_rate</t>
+  </si>
+  <si>
+    <t>0.0900</t>
+  </si>
+  <si>
+    <t>NJ base corporate income tax rate - 9% (11.5% for income &gt; $1M with surtax)</t>
+  </si>
+  <si>
+    <t>transaction_threshold</t>
+  </si>
+  <si>
+    <t>integer</t>
+  </si>
+  <si>
+    <t>200</t>
+  </si>
+  <si>
+    <t>Economic nexus transaction count threshold - Default 200</t>
+  </si>
+  <si>
+    <t>nj_result</t>
+  </si>
+  <si>
+    <t>entire_net_income</t>
   </si>
   <si>
     <t>0.0</t>
   </si>
   <si>
-    <t>State-specific additions: federal interest, IRC 199A addback, bonus depreciation, etc.</t>
-  </si>
-  <si>
-    <t>state_code</t>
-  </si>
-  <si>
-    <t>NJ</t>
-  </si>
-  <si>
-    <t>Two-letter state code - New Jersey</t>
-  </si>
-  <si>
-    <t>state_credits</t>
-  </si>
-  <si>
-    <t>State tax credits: R&amp;D, jobs, film, renewable energy, etc.</t>
-  </si>
-  <si>
-    <t>state_subtractions</t>
-  </si>
-  <si>
-    <t>State-specific subtractions: municipal interest, state taxes, state NOL, etc.</t>
-  </si>
-  <si>
-    <t>state_tax_rate</t>
-  </si>
-  <si>
-    <t>0.0900</t>
-  </si>
-  <si>
-    <t>NJ base corporate income tax rate - 9% (11.5% for income &gt; $1M with surtax)</t>
-  </si>
-  <si>
-    <t>transaction_threshold</t>
-  </si>
-  <si>
-    <t>integer</t>
-  </si>
-  <si>
-    <t>200</t>
-  </si>
-  <si>
-    <t>Economic nexus transaction count threshold - Default 200</t>
-  </si>
-  <si>
-    <t>result</t>
-  </si>
-  <si>
-    <t>(4 attributes)</t>
-  </si>
-  <si>
-    <t>nj_entire_net_income</t>
-  </si>
-  <si>
     <t>NJ entire net income (NJ term for taxable income base)</t>
   </si>
   <si>
-    <t>nj_surtax</t>
+    <t>surtax</t>
   </si>
   <si>
     <t>NJ surtax amount calculated (2.5% of entire net income &gt; $1M)</t>
   </si>
   <si>
-    <t>nj_surtax_rate</t>
+    <t>surtax_rate</t>
   </si>
   <si>
     <t>0.025</t>
@@ -392,7 +362,7 @@
     <t>NJ surtax rate (2.5% for corporations with income &gt; $1M)</t>
   </si>
   <si>
-    <t>nj_surtax_threshold</t>
+    <t>surtax_threshold</t>
   </si>
   <si>
     <t>1000000.0</t>
@@ -4300,14 +4270,14 @@
       <c r="B7" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="C7" s="10" t="s">
-        <v>90</v>
+      <c r="C7" s="11" t="s">
+        <v>102</v>
       </c>
       <c r="D7" s="8" t="s">
         <v>14</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F7" s="8" t="s">
         <v>14</v>
@@ -4316,7 +4286,7 @@
         <v>92</v>
       </c>
       <c r="H7" s="16" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I7" s="8" t="s">
         <v>14</v>
@@ -4335,48 +4305,26 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="C8" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="H8" s="16" t="s">
+      <c r="A8" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="I8" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="J8" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="K8" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="L8" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="M8" s="7" t="s">
-        <v>14</v>
-      </c>
+      <c r="B8" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="C8" s="6"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="6"/>
+      <c r="H8" s="6"/>
+      <c r="I8" s="6"/>
+      <c r="J8" s="6"/>
+      <c r="K8" s="6"/>
+      <c r="L8" s="6"/>
+      <c r="M8" s="6"/>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="7" t="s">
         <v>14</v>
       </c>
       <c r="B9" s="9" t="s">
@@ -4385,299 +4333,157 @@
       <c r="C9" s="11" t="s">
         <v>95</v>
       </c>
-      <c r="D9" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="F9" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="G9" s="8" t="s">
+      <c r="D9" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G9" s="7" t="s">
         <v>92</v>
       </c>
       <c r="H9" s="16" t="s">
-        <v>107</v>
-      </c>
-      <c r="I9" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="J9" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="K9" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="L9" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="M9" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="I9" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="J9" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="K9" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="L9" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="M9" s="7" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="8" t="s">
         <v>14</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C10" s="11" t="s">
         <v>95</v>
       </c>
-      <c r="D10" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G10" s="7" t="s">
+      <c r="D10" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G10" s="8" t="s">
         <v>92</v>
       </c>
       <c r="H10" s="16" t="s">
         <v>110</v>
       </c>
-      <c r="I10" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="J10" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="K10" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="L10" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="M10" s="7" t="s">
+      <c r="I10" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="J10" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="K10" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="L10" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="M10" s="8" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="7" t="s">
         <v>14</v>
       </c>
       <c r="B11" s="9" t="s">
         <v>111</v>
       </c>
       <c r="C11" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E11" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="D11" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E11" s="8" t="s">
+      <c r="F11" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="H11" s="16" t="s">
         <v>113</v>
       </c>
-      <c r="F11" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="G11" s="8" t="s">
+      <c r="I11" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="J11" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="K11" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="L11" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="M11" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G12" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="H11" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="I11" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="J11" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="K11" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="L11" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="M11" s="8" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="B12" s="6" t="s">
+      <c r="H12" s="16" t="s">
         <v>116</v>
       </c>
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="6"/>
-      <c r="G12" s="6"/>
-      <c r="H12" s="6"/>
-      <c r="I12" s="6"/>
-      <c r="J12" s="6"/>
-      <c r="K12" s="6"/>
-      <c r="L12" s="6"/>
-      <c r="M12" s="6"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B13" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="C13" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="F13" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G13" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="H13" s="16" t="s">
-        <v>118</v>
-      </c>
-      <c r="I13" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="J13" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="K13" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="L13" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="M13" s="7" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B14" s="9" t="s">
-        <v>119</v>
-      </c>
-      <c r="C14" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="D14" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E14" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="F14" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="G14" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="H14" s="16" t="s">
-        <v>120</v>
-      </c>
-      <c r="I14" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="J14" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="K14" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="L14" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="M14" s="8" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B15" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="C15" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E15" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="F15" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G15" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="H15" s="16" t="s">
-        <v>123</v>
-      </c>
-      <c r="I15" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="J15" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="K15" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="L15" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="M15" s="7" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B16" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="C16" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="D16" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E16" s="8" t="s">
-        <v>125</v>
-      </c>
-      <c r="F16" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="G16" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="H16" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="I16" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="J16" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="K16" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="L16" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="M16" s="8" t="s">
+      <c r="I12" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="J12" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="K12" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="L12" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="M12" s="8" t="s">
         <v>14</v>
       </c>
     </row>
